--- a/materiais/cota-parte-icms-municipios-es.xlsx
+++ b/materiais/cota-parte-icms-municipios-es.xlsx
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Síntese do levantamento · Eduardo Reis Araújo · gerado em 08/07/2026</t>
+          <t>Síntese do levantamento · Eduardo Reis Araújo · gerado em 07/09/2026</t>
         </is>
       </c>
     </row>
